--- a/artfynd/A 38933-2024 artfynd.xlsx
+++ b/artfynd/A 38933-2024 artfynd.xlsx
@@ -1681,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119938511</v>
+        <v>119940412</v>
       </c>
       <c r="B11" t="n">
-        <v>105009</v>
+        <v>91185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,31 +1697,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1729,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575124</v>
+        <v>575078</v>
       </c>
       <c r="R11" t="n">
-        <v>6416267</v>
+        <v>6416348</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119940412</v>
+        <v>119938511</v>
       </c>
       <c r="B12" t="n">
-        <v>91185</v>
+        <v>105009</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,34 +1811,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575078</v>
+        <v>575124</v>
       </c>
       <c r="R12" t="n">
-        <v>6416348</v>
+        <v>6416267</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119940194</v>
+        <v>119938708</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3361,25 +3361,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575107</v>
+        <v>575125</v>
       </c>
       <c r="R26" t="n">
-        <v>6416344</v>
+        <v>6416267</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119938708</v>
+        <v>119940194</v>
       </c>
       <c r="B27" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3472,25 +3472,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575125</v>
+        <v>575107</v>
       </c>
       <c r="R27" t="n">
-        <v>6416267</v>
+        <v>6416344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119968180</v>
+        <v>119968253</v>
       </c>
       <c r="B41" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5026,38 +5026,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5065,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575071</v>
+        <v>575057</v>
       </c>
       <c r="R41" t="n">
-        <v>6416392</v>
+        <v>6416397</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5128,10 +5125,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119968253</v>
+        <v>119968180</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5140,35 +5137,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575057</v>
+        <v>575071</v>
       </c>
       <c r="R42" t="n">
-        <v>6416397</v>
+        <v>6416392</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 38933-2024 artfynd.xlsx
+++ b/artfynd/A 38933-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119940174</v>
+        <v>119938648</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575106</v>
+        <v>575128</v>
       </c>
       <c r="R2" t="n">
-        <v>6416345</v>
+        <v>6416263</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119940424</v>
+        <v>119938612</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575087</v>
+        <v>575124</v>
       </c>
       <c r="R3" t="n">
-        <v>6416383</v>
+        <v>6416277</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119938634</v>
+        <v>119940306</v>
       </c>
       <c r="B4" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575122</v>
+        <v>575110</v>
       </c>
       <c r="R4" t="n">
-        <v>6416273</v>
+        <v>6416366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119938478</v>
+        <v>119940174</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575109</v>
+        <v>575106</v>
       </c>
       <c r="R5" t="n">
-        <v>6416284</v>
+        <v>6416345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,17 +1094,13 @@
           <t>2024-09-23</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat träd</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119938447</v>
+        <v>119938708</v>
       </c>
       <c r="B6" t="n">
-        <v>57316</v>
+        <v>105009</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,39 +1131,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575113</v>
+        <v>575125</v>
       </c>
       <c r="R6" t="n">
-        <v>6416259</v>
+        <v>6416267</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,6 +1211,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119938537</v>
+        <v>119940483</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1285,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575112</v>
+        <v>575091</v>
       </c>
       <c r="R7" t="n">
-        <v>6416276</v>
+        <v>6416367</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119938467</v>
+        <v>119938585</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1396,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575080</v>
+        <v>575119</v>
       </c>
       <c r="R8" t="n">
-        <v>6416290</v>
+        <v>6416261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119940483</v>
+        <v>119940254</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1507,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575091</v>
+        <v>575103</v>
       </c>
       <c r="R9" t="n">
-        <v>6416367</v>
+        <v>6416355</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119940492</v>
+        <v>119940401</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1618,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575084</v>
+        <v>575085</v>
       </c>
       <c r="R10" t="n">
-        <v>6416347</v>
+        <v>6416375</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119940412</v>
+        <v>119938631</v>
       </c>
       <c r="B11" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,38 +1686,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1732,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575078</v>
+        <v>575122</v>
       </c>
       <c r="R11" t="n">
-        <v>6416348</v>
+        <v>6416273</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119938511</v>
+        <v>119938447</v>
       </c>
       <c r="B12" t="n">
-        <v>105009</v>
+        <v>57316</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,35 +1797,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100048</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1843,13 +1837,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575124</v>
+        <v>575113</v>
       </c>
       <c r="R12" t="n">
-        <v>6416267</v>
+        <v>6416259</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1881,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1906,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119940216</v>
+        <v>119938511</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,25 +1911,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1954,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575098</v>
+        <v>575124</v>
       </c>
       <c r="R13" t="n">
-        <v>6416346</v>
+        <v>6416267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119940460</v>
+        <v>119940361</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2065,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575108</v>
+        <v>575097</v>
       </c>
       <c r="R14" t="n">
-        <v>6416341</v>
+        <v>6416366</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119940254</v>
+        <v>119940391</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2176,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575103</v>
+        <v>575083</v>
       </c>
       <c r="R15" t="n">
-        <v>6416355</v>
+        <v>6416386</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119940306</v>
+        <v>119940424</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2287,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575110</v>
+        <v>575087</v>
       </c>
       <c r="R16" t="n">
-        <v>6416366</v>
+        <v>6416383</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119938631</v>
+        <v>119938478</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,35 +2355,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2398,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575122</v>
+        <v>575109</v>
       </c>
       <c r="R17" t="n">
-        <v>6416273</v>
+        <v>6416284</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,13 +2429,17 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bearbetat träd</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2461,7 +2458,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119938648</v>
+        <v>119938720</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2509,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575128</v>
+        <v>575115</v>
       </c>
       <c r="R18" t="n">
-        <v>6416263</v>
+        <v>6416279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,7 +2569,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119938554</v>
+        <v>119940492</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2620,10 +2617,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575121</v>
+        <v>575084</v>
       </c>
       <c r="R19" t="n">
-        <v>6416272</v>
+        <v>6416347</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119938720</v>
+        <v>119938634</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2695,25 +2692,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2728,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575115</v>
+        <v>575122</v>
       </c>
       <c r="R20" t="n">
-        <v>6416279</v>
+        <v>6416273</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2794,7 +2791,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119940401</v>
+        <v>119940216</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2842,10 +2839,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575085</v>
+        <v>575098</v>
       </c>
       <c r="R21" t="n">
-        <v>6416375</v>
+        <v>6416346</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119940361</v>
+        <v>119940412</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,35 +2914,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575097</v>
+        <v>575078</v>
       </c>
       <c r="R22" t="n">
-        <v>6416366</v>
+        <v>6416348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,7 +3016,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119938585</v>
+        <v>119940460</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575119</v>
+        <v>575108</v>
       </c>
       <c r="R23" t="n">
-        <v>6416261</v>
+        <v>6416341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119938612</v>
+        <v>119938554</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575124</v>
+        <v>575121</v>
       </c>
       <c r="R24" t="n">
-        <v>6416277</v>
+        <v>6416272</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119940391</v>
+        <v>119940194</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575083</v>
+        <v>575107</v>
       </c>
       <c r="R25" t="n">
-        <v>6416386</v>
+        <v>6416344</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119938708</v>
+        <v>119938467</v>
       </c>
       <c r="B26" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3361,25 +3361,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575125</v>
+        <v>575080</v>
       </c>
       <c r="R26" t="n">
-        <v>6416267</v>
+        <v>6416290</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119940194</v>
+        <v>119938537</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575107</v>
+        <v>575112</v>
       </c>
       <c r="R27" t="n">
-        <v>6416344</v>
+        <v>6416276</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119967969</v>
+        <v>119968099</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575060</v>
+        <v>575074</v>
       </c>
       <c r="R28" t="n">
-        <v>6416409</v>
+        <v>6416404</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119968142</v>
+        <v>119968063</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3694,25 +3694,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575068</v>
+        <v>575065</v>
       </c>
       <c r="R29" t="n">
-        <v>6416399</v>
+        <v>6416381</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119968073</v>
+        <v>119967969</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575073</v>
+        <v>575060</v>
       </c>
       <c r="R30" t="n">
-        <v>6416399</v>
+        <v>6416409</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3904,7 +3904,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119968013</v>
+        <v>119968228</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575079</v>
+        <v>575068</v>
       </c>
       <c r="R31" t="n">
-        <v>6416407</v>
+        <v>6416351</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4015,7 +4015,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119968222</v>
+        <v>119968206</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575078</v>
+        <v>575059</v>
       </c>
       <c r="R32" t="n">
-        <v>6416388</v>
+        <v>6416376</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119967859</v>
+        <v>119968222</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575055</v>
+        <v>575078</v>
       </c>
       <c r="R33" t="n">
-        <v>6416371</v>
+        <v>6416388</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119968242</v>
+        <v>119967912</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575057</v>
+        <v>575038</v>
       </c>
       <c r="R34" t="n">
-        <v>6416399</v>
+        <v>6416393</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4348,10 +4348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119968155</v>
+        <v>119968025</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4360,25 +4360,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575062</v>
+        <v>575077</v>
       </c>
       <c r="R35" t="n">
-        <v>6416393</v>
+        <v>6416406</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,7 +4459,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119967912</v>
+        <v>119968032</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575038</v>
+        <v>575084</v>
       </c>
       <c r="R36" t="n">
-        <v>6416393</v>
+        <v>6416405</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119968032</v>
+        <v>119968180</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4582,35 +4582,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4618,10 +4621,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575084</v>
+        <v>575071</v>
       </c>
       <c r="R37" t="n">
-        <v>6416405</v>
+        <v>6416392</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4681,7 +4684,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119968086</v>
+        <v>119967849</v>
       </c>
       <c r="B38" t="n">
         <v>97907</v>
@@ -4729,10 +4732,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575084</v>
+        <v>575047</v>
       </c>
       <c r="R38" t="n">
-        <v>6416402</v>
+        <v>6416373</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4792,7 +4795,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119968206</v>
+        <v>119968155</v>
       </c>
       <c r="B39" t="n">
         <v>97907</v>
@@ -4840,10 +4843,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575059</v>
+        <v>575062</v>
       </c>
       <c r="R39" t="n">
-        <v>6416376</v>
+        <v>6416393</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4903,7 +4906,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119968237</v>
+        <v>119967959</v>
       </c>
       <c r="B40" t="n">
         <v>97907</v>
@@ -4951,10 +4954,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575077</v>
+        <v>575073</v>
       </c>
       <c r="R40" t="n">
-        <v>6416389</v>
+        <v>6416397</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5014,10 +5017,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119968253</v>
+        <v>119968117</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5026,25 +5029,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5062,10 +5065,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575057</v>
+        <v>575074</v>
       </c>
       <c r="R41" t="n">
-        <v>6416397</v>
+        <v>6416404</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5125,10 +5128,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119968180</v>
+        <v>119968242</v>
       </c>
       <c r="B42" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5137,38 +5140,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575071</v>
+        <v>575057</v>
       </c>
       <c r="R42" t="n">
-        <v>6416392</v>
+        <v>6416399</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119968228</v>
+        <v>119967895</v>
       </c>
       <c r="B43" t="n">
         <v>97907</v>
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575068</v>
+        <v>575046</v>
       </c>
       <c r="R43" t="n">
-        <v>6416351</v>
+        <v>6416362</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5350,7 +5350,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119968216</v>
+        <v>119968013</v>
       </c>
       <c r="B44" t="n">
         <v>97907</v>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575074</v>
+        <v>575079</v>
       </c>
       <c r="R44" t="n">
-        <v>6416403</v>
+        <v>6416407</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119967895</v>
+        <v>119968073</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575046</v>
+        <v>575073</v>
       </c>
       <c r="R45" t="n">
-        <v>6416362</v>
+        <v>6416399</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119967959</v>
+        <v>119968129</v>
       </c>
       <c r="B46" t="n">
         <v>97907</v>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575073</v>
+        <v>575074</v>
       </c>
       <c r="R46" t="n">
-        <v>6416397</v>
+        <v>6416383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5683,7 +5683,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119967982</v>
+        <v>119968237</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575075</v>
+        <v>575077</v>
       </c>
       <c r="R47" t="n">
-        <v>6416412</v>
+        <v>6416389</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119967849</v>
+        <v>119968216</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575047</v>
+        <v>575074</v>
       </c>
       <c r="R48" t="n">
-        <v>6416373</v>
+        <v>6416403</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5905,10 +5905,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119968025</v>
+        <v>119967996</v>
       </c>
       <c r="B49" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5917,25 +5917,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575077</v>
+        <v>575074</v>
       </c>
       <c r="R49" t="n">
         <v>6416406</v>
@@ -6016,10 +6016,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119968117</v>
+        <v>119967859</v>
       </c>
       <c r="B50" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6028,25 +6028,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575074</v>
+        <v>575055</v>
       </c>
       <c r="R50" t="n">
-        <v>6416404</v>
+        <v>6416371</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6127,7 +6127,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119968129</v>
+        <v>119968086</v>
       </c>
       <c r="B51" t="n">
         <v>97907</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575074</v>
+        <v>575084</v>
       </c>
       <c r="R51" t="n">
-        <v>6416383</v>
+        <v>6416402</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6238,10 +6238,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119968063</v>
+        <v>119967982</v>
       </c>
       <c r="B52" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6250,25 +6250,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575065</v>
+        <v>575075</v>
       </c>
       <c r="R52" t="n">
-        <v>6416381</v>
+        <v>6416412</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119967996</v>
+        <v>119968194</v>
       </c>
       <c r="B53" t="n">
         <v>97907</v>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575074</v>
+        <v>575057</v>
       </c>
       <c r="R53" t="n">
-        <v>6416406</v>
+        <v>6416391</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119968099</v>
+        <v>119968142</v>
       </c>
       <c r="B54" t="n">
         <v>97907</v>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575074</v>
+        <v>575068</v>
       </c>
       <c r="R54" t="n">
-        <v>6416404</v>
+        <v>6416399</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6571,7 +6571,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119968194</v>
+        <v>119968253</v>
       </c>
       <c r="B55" t="n">
         <v>97907</v>
@@ -6622,7 +6622,7 @@
         <v>575057</v>
       </c>
       <c r="R55" t="n">
-        <v>6416391</v>
+        <v>6416397</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120018286</v>
+        <v>120018301</v>
       </c>
       <c r="B56" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6694,38 +6694,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6733,10 +6730,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574888</v>
+        <v>574873</v>
       </c>
       <c r="R56" t="n">
-        <v>6416303</v>
+        <v>6416285</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6796,7 +6793,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120018262</v>
+        <v>120018295</v>
       </c>
       <c r="B57" t="n">
         <v>97907</v>
@@ -6844,10 +6841,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574903</v>
+        <v>574891</v>
       </c>
       <c r="R57" t="n">
-        <v>6416284</v>
+        <v>6416277</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6907,10 +6904,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120018327</v>
+        <v>120018286</v>
       </c>
       <c r="B58" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6919,35 +6916,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6955,10 +6955,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574885</v>
+        <v>574888</v>
       </c>
       <c r="R58" t="n">
-        <v>6416309</v>
+        <v>6416303</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7018,10 +7018,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120018318</v>
+        <v>120018509</v>
       </c>
       <c r="B59" t="n">
-        <v>105009</v>
+        <v>57316</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7030,35 +7030,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>100048</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7066,13 +7070,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574885</v>
+        <v>574848</v>
       </c>
       <c r="R59" t="n">
-        <v>6416309</v>
+        <v>6416347</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7104,13 +7108,17 @@
           <t>2024-09-24</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>3:e dagen i rad med mindre hackspett i anmälan!</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7129,7 +7137,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120018301</v>
+        <v>120018327</v>
       </c>
       <c r="B60" t="n">
         <v>97907</v>
@@ -7177,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574873</v>
+        <v>574885</v>
       </c>
       <c r="R60" t="n">
-        <v>6416285</v>
+        <v>6416309</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7240,7 +7248,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120018272</v>
+        <v>120018262</v>
       </c>
       <c r="B61" t="n">
         <v>97907</v>
@@ -7288,10 +7296,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574891</v>
+        <v>574903</v>
       </c>
       <c r="R61" t="n">
-        <v>6416315</v>
+        <v>6416284</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7351,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120018509</v>
+        <v>120018272</v>
       </c>
       <c r="B62" t="n">
-        <v>57316</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7363,39 +7371,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7403,13 +7407,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574848</v>
+        <v>574891</v>
       </c>
       <c r="R62" t="n">
-        <v>6416347</v>
+        <v>6416315</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7441,17 +7445,13 @@
           <t>2024-09-24</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>3:e dagen i rad med mindre hackspett i anmälan!</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7585,10 +7585,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120018295</v>
+        <v>120018318</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7597,25 +7597,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574891</v>
+        <v>574885</v>
       </c>
       <c r="R64" t="n">
-        <v>6416277</v>
+        <v>6416309</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 38933-2024 artfynd.xlsx
+++ b/artfynd/A 38933-2024 artfynd.xlsx
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119940412</v>
+        <v>119940460</v>
       </c>
       <c r="B22" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,38 +2914,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2953,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575078</v>
+        <v>575108</v>
       </c>
       <c r="R22" t="n">
-        <v>6416348</v>
+        <v>6416341</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,7 +3013,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119940460</v>
+        <v>119938554</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -3064,10 +3061,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575108</v>
+        <v>575121</v>
       </c>
       <c r="R23" t="n">
-        <v>6416341</v>
+        <v>6416272</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,10 +3124,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119938554</v>
+        <v>119940412</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3139,35 +3136,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575121</v>
+        <v>575078</v>
       </c>
       <c r="R24" t="n">
-        <v>6416272</v>
+        <v>6416348</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -7018,10 +7018,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120018509</v>
+        <v>120018327</v>
       </c>
       <c r="B59" t="n">
-        <v>57316</v>
+        <v>97907</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7030,39 +7030,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7070,13 +7066,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574848</v>
+        <v>574885</v>
       </c>
       <c r="R59" t="n">
-        <v>6416347</v>
+        <v>6416309</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7108,17 +7104,13 @@
           <t>2024-09-24</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>3:e dagen i rad med mindre hackspett i anmälan!</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7137,7 +7129,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120018327</v>
+        <v>120018262</v>
       </c>
       <c r="B60" t="n">
         <v>97907</v>
@@ -7185,10 +7177,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574885</v>
+        <v>574903</v>
       </c>
       <c r="R60" t="n">
-        <v>6416309</v>
+        <v>6416284</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7248,10 +7240,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120018262</v>
+        <v>120018509</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>57316</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7260,35 +7252,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7296,13 +7292,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574903</v>
+        <v>574848</v>
       </c>
       <c r="R61" t="n">
-        <v>6416284</v>
+        <v>6416347</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7334,13 +7330,17 @@
           <t>2024-09-24</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>3:e dagen i rad med mindre hackspett i anmälan!</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
